--- a/data.mn/public/datasets/teachers-by-level.xlsx
+++ b/data.mn/public/datasets/teachers-by-level.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,282 +414,1281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>General educational schools</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>General educational schools - Female</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Kindergartens</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Kindergartens - Female</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Technical and vocational educational institutions</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Technical and vocational educational institutions - Female</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Total - Female</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Universities, institutes, colleges</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Universities, institutes, colleges - Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>2010</v>
-      </c>
-      <c r="C1" t="n">
-        <v>2011</v>
-      </c>
-      <c r="D1" t="n">
-        <v>2012</v>
-      </c>
-      <c r="E1" t="n">
-        <v>2013</v>
-      </c>
-      <c r="F1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="G1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="H1" t="n">
-        <v>2016</v>
-      </c>
-      <c r="I1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="K1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="L1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="M1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="N1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="O1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="P1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>General educational schools</t>
-        </is>
       </c>
       <c r="B2" t="n">
         <v>26358</v>
       </c>
       <c r="C2" t="n">
+        <v>21614</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4651</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4569</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1331</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40335</v>
+      </c>
+      <c r="I2" t="n">
+        <v>31688</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7183</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B3" t="n">
         <v>26492</v>
       </c>
+      <c r="C3" t="n">
+        <v>21717</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4907</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4813</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2093</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="H3" t="n">
+        <v>40787</v>
+      </c>
+      <c r="I3" t="n">
+        <v>32147</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7295</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B4" t="n">
+        <v>26863</v>
+      </c>
+      <c r="C4" t="n">
+        <v>21936</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5332</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5238</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2236</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1461</v>
+      </c>
+      <c r="H4" t="n">
+        <v>41762</v>
+      </c>
+      <c r="I4" t="n">
+        <v>33006</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7331</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B5" t="n">
+        <v>27205</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22051</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5895</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5773</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2498</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1608</v>
+      </c>
+      <c r="H5" t="n">
+        <v>42983</v>
+      </c>
+      <c r="I5" t="n">
+        <v>33974</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7385</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4542</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B6" t="n">
+        <v>27449</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22285</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6158</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6046</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2327</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1497</v>
+      </c>
+      <c r="H6" t="n">
+        <v>43462</v>
+      </c>
+      <c r="I6" t="n">
+        <v>34456</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7528</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B7" t="n">
+        <v>28490</v>
+      </c>
+      <c r="C7" t="n">
+        <v>23120</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6833</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6686</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2504</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1621</v>
+      </c>
+      <c r="H7" t="n">
+        <v>44948</v>
+      </c>
+      <c r="I7" t="n">
+        <v>35795</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7121</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B8" t="n">
+        <v>28889</v>
+      </c>
+      <c r="C8" t="n">
+        <v>23479</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7302</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7142</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2510</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1574</v>
+      </c>
+      <c r="H8" t="n">
+        <v>45618</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36325</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6917</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B9" t="n">
+        <v>29242</v>
+      </c>
+      <c r="C9" t="n">
+        <v>23876</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7745</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7542</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2230</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1369</v>
+      </c>
+      <c r="H9" t="n">
+        <v>45941</v>
+      </c>
+      <c r="I9" t="n">
+        <v>36784</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6724</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3997</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="n">
+        <v>30411</v>
+      </c>
+      <c r="C10" t="n">
+        <v>24879</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7843</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7609</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2469</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1564</v>
+      </c>
+      <c r="H10" t="n">
+        <v>47391</v>
+      </c>
+      <c r="I10" t="n">
+        <v>38080</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6668</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B11" t="n">
+        <v>32085</v>
+      </c>
+      <c r="C11" t="n">
+        <v>26149</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8068</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7809</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2388</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1551</v>
+      </c>
+      <c r="H11" t="n">
+        <v>49871</v>
+      </c>
+      <c r="I11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7330</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4491</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B12" t="n">
+        <v>34073</v>
+      </c>
+      <c r="C12" t="n">
+        <v>27729</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8827</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8516</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2242</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1433</v>
+      </c>
+      <c r="H12" t="n">
+        <v>52285</v>
+      </c>
+      <c r="I12" t="n">
+        <v>41992</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7143</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>35110</v>
+      </c>
+      <c r="C13" t="n">
+        <v>28642</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8824</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8487</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2124</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1387</v>
+      </c>
+      <c r="H13" t="n">
+        <v>52160</v>
+      </c>
+      <c r="I13" t="n">
+        <v>42256</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6102</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="n">
+        <v>36118</v>
+      </c>
+      <c r="C14" t="n">
+        <v>29546</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9450</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9098</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2252</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1460</v>
+      </c>
+      <c r="H14" t="n">
+        <v>52989</v>
+      </c>
+      <c r="I14" t="n">
+        <v>43273</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5169</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3169</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="n">
+        <v>36993</v>
+      </c>
+      <c r="C15" t="n">
+        <v>30341</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9733</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9332</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2351</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1524</v>
+      </c>
+      <c r="H15" t="n">
+        <v>54189</v>
+      </c>
+      <c r="I15" t="n">
+        <v>44338</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5112</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="n">
+        <v>37770</v>
+      </c>
+      <c r="C16" t="n">
+        <v>31161</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9945</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9496</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2140</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1391</v>
+      </c>
+      <c r="H16" t="n">
+        <v>55006</v>
+      </c>
+      <c r="I16" t="n">
+        <v>45191</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>39126</v>
+      </c>
+      <c r="C17" t="n">
+        <v>32292</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10298</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9819</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2163</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H17" t="n">
+        <v>56853</v>
+      </c>
+      <c r="I17" t="n">
+        <v>46753</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5266</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Бүгд</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Бүгд - Эмэгтэй</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ерөнхий боловсролын сургууль</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ерөнхий боловсролын сургууль - Эмэгтэй</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Их, дээд сургууль, коллеж</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Их, дээд сургууль, коллеж - Эмэгтэй</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Техникийн болон мэргэжлийн боловсролын сургалтын байгууллага</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Техникийн болон мэргэжлийн боловсролын сургалтын байгууллага - Эмэгтэй</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Цэцэрлэг</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Цэцэрлэг - Эмэгтэй</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B2" t="n">
+        <v>40335</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31688</v>
+      </c>
       <c r="D2" t="n">
+        <v>26358</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21614</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7183</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4174</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1331</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4651</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4569</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B3" t="n">
+        <v>40787</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32147</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26492</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21717</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7295</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4287</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2093</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4907</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4813</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B4" t="n">
+        <v>41762</v>
+      </c>
+      <c r="C4" t="n">
+        <v>33006</v>
+      </c>
+      <c r="D4" t="n">
         <v>26863</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E4" t="n">
+        <v>21936</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7331</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4371</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2236</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1461</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5332</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5238</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B5" t="n">
+        <v>42983</v>
+      </c>
+      <c r="C5" t="n">
+        <v>33974</v>
+      </c>
+      <c r="D5" t="n">
         <v>27205</v>
       </c>
-      <c r="F2" t="n">
+      <c r="E5" t="n">
+        <v>22051</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7385</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4542</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2498</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1608</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5895</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5773</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43462</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34456</v>
+      </c>
+      <c r="D6" t="n">
         <v>27449</v>
       </c>
-      <c r="G2" t="n">
+      <c r="E6" t="n">
+        <v>22285</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7528</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4628</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2327</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1497</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6158</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6046</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B7" t="n">
+        <v>44948</v>
+      </c>
+      <c r="C7" t="n">
+        <v>35795</v>
+      </c>
+      <c r="D7" t="n">
         <v>28490</v>
       </c>
-      <c r="H2" t="n">
+      <c r="E7" t="n">
+        <v>23120</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7121</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4368</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2504</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1621</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6833</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6686</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B8" t="n">
+        <v>45618</v>
+      </c>
+      <c r="C8" t="n">
+        <v>36325</v>
+      </c>
+      <c r="D8" t="n">
         <v>28889</v>
       </c>
-      <c r="I2" t="n">
+      <c r="E8" t="n">
+        <v>23479</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6917</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4130</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2510</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1574</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7302</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7142</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B9" t="n">
+        <v>45941</v>
+      </c>
+      <c r="C9" t="n">
+        <v>36784</v>
+      </c>
+      <c r="D9" t="n">
         <v>29242</v>
       </c>
-      <c r="J2" t="n">
+      <c r="E9" t="n">
+        <v>23876</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6724</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3997</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2230</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1369</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7745</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7542</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="n">
+        <v>47391</v>
+      </c>
+      <c r="C10" t="n">
+        <v>38080</v>
+      </c>
+      <c r="D10" t="n">
         <v>30411</v>
       </c>
-      <c r="K2" t="n">
+      <c r="E10" t="n">
+        <v>24879</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6668</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4028</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2469</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1564</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7843</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7609</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B11" t="n">
+        <v>49871</v>
+      </c>
+      <c r="C11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D11" t="n">
         <v>32085</v>
       </c>
-      <c r="L2" t="n">
+      <c r="E11" t="n">
+        <v>26149</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7330</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4491</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2388</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8068</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7809</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B12" t="n">
+        <v>52285</v>
+      </c>
+      <c r="C12" t="n">
+        <v>41992</v>
+      </c>
+      <c r="D12" t="n">
         <v>34073</v>
       </c>
-      <c r="M2" t="n">
+      <c r="E12" t="n">
+        <v>27729</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7143</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4314</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2242</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1433</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8827</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8516</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>52160</v>
+      </c>
+      <c r="C13" t="n">
+        <v>42256</v>
+      </c>
+      <c r="D13" t="n">
         <v>35110</v>
       </c>
-      <c r="N2" t="n">
+      <c r="E13" t="n">
+        <v>28642</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6102</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3740</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2124</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1387</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8824</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8487</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="n">
+        <v>52989</v>
+      </c>
+      <c r="C14" t="n">
+        <v>43273</v>
+      </c>
+      <c r="D14" t="n">
         <v>36118</v>
       </c>
-      <c r="O2" t="n">
+      <c r="E14" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5169</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3169</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2252</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1460</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9450</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9098</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="n">
+        <v>54189</v>
+      </c>
+      <c r="C15" t="n">
+        <v>44338</v>
+      </c>
+      <c r="D15" t="n">
         <v>36993</v>
       </c>
-      <c r="P2" t="n">
+      <c r="E15" t="n">
+        <v>30341</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5112</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3141</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2351</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1524</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9733</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9332</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="n">
+        <v>55006</v>
+      </c>
+      <c r="C16" t="n">
+        <v>45191</v>
+      </c>
+      <c r="D16" t="n">
         <v>37770</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="E16" t="n">
+        <v>31161</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3143</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2140</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1391</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9945</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9496</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56853</v>
+      </c>
+      <c r="C17" t="n">
+        <v>46753</v>
+      </c>
+      <c r="D17" t="n">
         <v>39126</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Kindergartens</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4651</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4907</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5332</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5895</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6158</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6833</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7302</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7745</v>
-      </c>
-      <c r="J3" t="n">
-        <v>7843</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8068</v>
-      </c>
-      <c r="L3" t="n">
-        <v>8827</v>
-      </c>
-      <c r="M3" t="n">
-        <v>8824</v>
-      </c>
-      <c r="N3" t="n">
-        <v>9450</v>
-      </c>
-      <c r="O3" t="n">
-        <v>9733</v>
-      </c>
-      <c r="P3" t="n">
-        <v>9945</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="E17" t="n">
+        <v>32292</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5266</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3242</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2163</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="J17" t="n">
         <v>10298</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Technical and vocational educational institutions</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2143</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2093</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2236</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2498</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2327</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2504</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2510</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2230</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2469</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2388</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2242</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2124</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2252</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2351</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2140</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2163</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Universities, institutes, colleges</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7183</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7295</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7331</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7385</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7528</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7121</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6917</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6724</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6668</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7330</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7143</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6102</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5169</v>
-      </c>
-      <c r="O5" t="n">
-        <v>5112</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5151</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5266</v>
+      <c r="K17" t="n">
+        <v>9819</v>
       </c>
     </row>
   </sheetData>
